--- a/article/家庭财务管理手册2026.xlsx
+++ b/article/家庭财务管理手册2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\18717\Documents\GitHub\luyao.github.io\article\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\baoyaoyao\Downloads\luyao.github.io-main\luyao.github.io-main\article\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E6C42A8-E034-49D2-85CE-A801A5E85B12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20542B1F-ABFE-44A9-B959-CCED2AD5AEA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="680" yWindow="680" windowWidth="2370" windowHeight="560" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1、收入结余表" sheetId="2" r:id="rId1"/>
@@ -27,6 +27,9 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -1222,7 +1225,7 @@
                   <c:v>5940295.1699999999</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>7124085.7999999998</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0</c:v>
@@ -2680,13 +2683,16 @@
       <c r="L4" s="25"/>
       <c r="M4" s="28"/>
       <c r="N4" s="25">
-        <f>'2、存量资产-y'!B27+'3、存量资产-k'!B14</f>
-        <v>0</v>
+        <f>'2、存量资产-y'!C26+'3、存量资产-k'!C13</f>
+        <v>7124085.7999999998</v>
       </c>
       <c r="O4" s="37">
-        <v>6500000</v>
-      </c>
-      <c r="P4" s="31"/>
+        <v>8000000</v>
+      </c>
+      <c r="P4" s="31">
+        <f>N4/O4</f>
+        <v>0.89051072499999995</v>
+      </c>
     </row>
     <row r="5" spans="2:17" ht="24.65" customHeight="1">
       <c r="B5" s="17">
@@ -3066,7 +3072,9 @@
       <c r="B2" s="6">
         <v>11501</v>
       </c>
-      <c r="C2" s="6"/>
+      <c r="C2" s="6">
+        <v>11724</v>
+      </c>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
       <c r="F2" s="6"/>
@@ -3086,7 +3094,9 @@
       <c r="B3" s="6">
         <v>147022.85999999999</v>
       </c>
-      <c r="C3" s="6"/>
+      <c r="C3" s="6">
+        <v>137526</v>
+      </c>
       <c r="D3" s="7"/>
       <c r="E3" s="7"/>
       <c r="F3" s="7"/>
@@ -3104,7 +3114,9 @@
         <v>22</v>
       </c>
       <c r="B4" s="6"/>
-      <c r="C4" s="6"/>
+      <c r="C4" s="6">
+        <v>32584</v>
+      </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
       <c r="F4" s="6"/>
@@ -3124,7 +3136,9 @@
       <c r="B5" s="6">
         <v>8519.66</v>
       </c>
-      <c r="C5" s="6"/>
+      <c r="C5" s="6">
+        <v>988.8</v>
+      </c>
       <c r="D5" s="7"/>
       <c r="E5" s="7"/>
       <c r="F5" s="7"/>
@@ -3144,7 +3158,9 @@
       <c r="B6" s="6">
         <v>112738.66</v>
       </c>
-      <c r="C6" s="6"/>
+      <c r="C6" s="6">
+        <v>142072</v>
+      </c>
       <c r="D6" s="6"/>
       <c r="E6" s="6"/>
       <c r="F6" s="6"/>
@@ -3184,7 +3200,9 @@
       <c r="B8" s="6">
         <v>32475.64</v>
       </c>
-      <c r="C8" s="6"/>
+      <c r="C8" s="6">
+        <v>32682</v>
+      </c>
       <c r="D8" s="6"/>
       <c r="E8" s="6"/>
       <c r="F8" s="6"/>
@@ -3222,7 +3240,9 @@
       <c r="B10" s="6">
         <v>10749</v>
       </c>
-      <c r="C10" s="6"/>
+      <c r="C10" s="6">
+        <v>17075</v>
+      </c>
       <c r="D10" s="6"/>
       <c r="E10" s="6"/>
       <c r="F10" s="6"/>
@@ -3242,17 +3262,39 @@
       <c r="B11" s="6">
         <v>500000</v>
       </c>
-      <c r="C11" s="6"/>
-      <c r="D11" s="6"/>
-      <c r="E11" s="6"/>
-      <c r="F11" s="6"/>
-      <c r="G11" s="6"/>
-      <c r="H11" s="6"/>
-      <c r="I11" s="6"/>
-      <c r="J11" s="6"/>
-      <c r="K11" s="6"/>
-      <c r="L11" s="6"/>
-      <c r="M11" s="6"/>
+      <c r="C11" s="6">
+        <v>500000</v>
+      </c>
+      <c r="D11" s="6">
+        <v>500000</v>
+      </c>
+      <c r="E11" s="6">
+        <v>500000</v>
+      </c>
+      <c r="F11" s="6">
+        <v>500000</v>
+      </c>
+      <c r="G11" s="6">
+        <v>500000</v>
+      </c>
+      <c r="H11" s="6">
+        <v>500000</v>
+      </c>
+      <c r="I11" s="6">
+        <v>500000</v>
+      </c>
+      <c r="J11" s="6">
+        <v>500000</v>
+      </c>
+      <c r="K11" s="6">
+        <v>500000</v>
+      </c>
+      <c r="L11" s="6">
+        <v>500000</v>
+      </c>
+      <c r="M11" s="6">
+        <v>500000</v>
+      </c>
       <c r="N11" s="15"/>
     </row>
     <row r="12" spans="1:14" ht="20.5" customHeight="1">
@@ -3262,17 +3304,39 @@
       <c r="B12" s="6">
         <v>500000</v>
       </c>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="6"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="6"/>
-      <c r="I12" s="6"/>
-      <c r="J12" s="6"/>
-      <c r="K12" s="6"/>
-      <c r="L12" s="6"/>
-      <c r="M12" s="6"/>
+      <c r="C12" s="6">
+        <v>500000</v>
+      </c>
+      <c r="D12" s="6">
+        <v>500000</v>
+      </c>
+      <c r="E12" s="6">
+        <v>500000</v>
+      </c>
+      <c r="F12" s="6">
+        <v>500000</v>
+      </c>
+      <c r="G12" s="6">
+        <v>500000</v>
+      </c>
+      <c r="H12" s="6">
+        <v>500000</v>
+      </c>
+      <c r="I12" s="6">
+        <v>500000</v>
+      </c>
+      <c r="J12" s="6">
+        <v>500000</v>
+      </c>
+      <c r="K12" s="6">
+        <v>500000</v>
+      </c>
+      <c r="L12" s="6">
+        <v>500000</v>
+      </c>
+      <c r="M12" s="6">
+        <v>500000</v>
+      </c>
       <c r="N12" s="15"/>
     </row>
     <row r="13" spans="1:14" ht="20.5" customHeight="1">
@@ -3282,7 +3346,9 @@
       <c r="B13" s="6">
         <v>19988.490000000002</v>
       </c>
-      <c r="C13" s="6"/>
+      <c r="C13" s="6">
+        <v>19935</v>
+      </c>
       <c r="D13" s="6"/>
       <c r="E13" s="6"/>
       <c r="F13" s="6"/>
@@ -3302,7 +3368,9 @@
       <c r="B14" s="6">
         <v>368986.86</v>
       </c>
-      <c r="C14" s="6"/>
+      <c r="C14" s="6">
+        <v>367684</v>
+      </c>
       <c r="D14" s="6"/>
       <c r="E14" s="6"/>
       <c r="F14" s="6"/>
@@ -3322,7 +3390,9 @@
       <c r="B15" s="6">
         <v>32279</v>
       </c>
-      <c r="C15" s="6"/>
+      <c r="C15" s="6">
+        <v>32226</v>
+      </c>
       <c r="D15" s="6"/>
       <c r="E15" s="6"/>
       <c r="F15" s="6"/>
@@ -3342,7 +3412,9 @@
       <c r="B16" s="6">
         <v>102080</v>
       </c>
-      <c r="C16" s="6"/>
+      <c r="C16" s="6">
+        <v>101693</v>
+      </c>
       <c r="D16" s="6"/>
       <c r="E16" s="6"/>
       <c r="F16" s="6"/>
@@ -3365,47 +3437,47 @@
       </c>
       <c r="C17" s="9">
         <f t="shared" ref="C17:M17" si="0">SUM(C2:C16)</f>
-        <v>0</v>
+        <v>1896189.8</v>
       </c>
       <c r="D17" s="9">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="E17" s="9">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="F17" s="9">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="G17" s="9">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="H17" s="9">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="I17" s="9">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="J17" s="9">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="K17" s="9">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="L17" s="9">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="M17" s="9">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="N17" s="15"/>
     </row>
@@ -3416,7 +3488,9 @@
       <c r="B18" s="6">
         <v>135584</v>
       </c>
-      <c r="C18" s="6"/>
+      <c r="C18" s="6">
+        <v>135731</v>
+      </c>
       <c r="D18" s="6"/>
       <c r="E18" s="6"/>
       <c r="F18" s="6"/>
@@ -3436,7 +3510,9 @@
       <c r="B19" s="6">
         <v>133109</v>
       </c>
-      <c r="C19" s="6"/>
+      <c r="C19" s="6">
+        <v>136839</v>
+      </c>
       <c r="D19" s="6"/>
       <c r="E19" s="6"/>
       <c r="F19" s="6"/>
@@ -3456,7 +3532,9 @@
       <c r="B20" s="6">
         <v>22604</v>
       </c>
-      <c r="C20" s="6"/>
+      <c r="C20" s="6">
+        <v>22907</v>
+      </c>
       <c r="D20" s="7"/>
       <c r="E20" s="7"/>
       <c r="F20" s="7"/>
@@ -3479,7 +3557,7 @@
       </c>
       <c r="C21" s="11">
         <f t="shared" ref="C21:M21" si="1">SUM(C18:C20)</f>
-        <v>0</v>
+        <v>295477</v>
       </c>
       <c r="D21" s="11">
         <f t="shared" si="1"/>
@@ -3623,47 +3701,47 @@
       </c>
       <c r="C25" s="13">
         <f t="shared" ref="C25:M25" si="3">SUM(C17,C21)</f>
-        <v>0</v>
+        <v>2191666.7999999998</v>
       </c>
       <c r="D25" s="13">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="E25" s="13">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="F25" s="13">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="G25" s="13">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="H25" s="13">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="I25" s="13">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="J25" s="13">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="K25" s="13">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="L25" s="13">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="M25" s="13">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="N25" s="15"/>
     </row>
@@ -3677,47 +3755,47 @@
       </c>
       <c r="C26" s="13">
         <f t="shared" ref="C26:M26" si="4">C25-C24</f>
-        <v>0</v>
+        <v>2191666.7999999998</v>
       </c>
       <c r="D26" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="E26" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="F26" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="G26" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="H26" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="I26" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="J26" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="K26" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="L26" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="M26" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="N26" s="15"/>
     </row>
@@ -3794,7 +3872,10 @@
         <f>490768*7</f>
         <v>3435376</v>
       </c>
-      <c r="C2" s="6"/>
+      <c r="C2" s="6">
+        <f>592893*7</f>
+        <v>4150251</v>
+      </c>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
       <c r="F2" s="6"/>
@@ -3815,7 +3896,10 @@
         <f>155000+43677+1565+1234+307</f>
         <v>201783</v>
       </c>
-      <c r="C3" s="6"/>
+      <c r="C3" s="6">
+        <f>396647+1521+1154+304+198050</f>
+        <v>597676</v>
+      </c>
       <c r="D3" s="7"/>
       <c r="E3" s="7"/>
       <c r="F3" s="7"/>
@@ -3835,7 +3919,9 @@
       <c r="B4" s="6">
         <v>3750</v>
       </c>
-      <c r="C4" s="6"/>
+      <c r="C4" s="6">
+        <v>3883</v>
+      </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
       <c r="F4" s="6"/>
@@ -3858,7 +3944,7 @@
       </c>
       <c r="C5" s="9">
         <f t="shared" ref="C5:M5" si="0">SUM(C2:C4)</f>
-        <v>0</v>
+        <v>4751810</v>
       </c>
       <c r="D5" s="9">
         <f t="shared" si="0"/>
@@ -3910,7 +3996,10 @@
         <f>33429+58692+45931</f>
         <v>138052</v>
       </c>
-      <c r="C6" s="6"/>
+      <c r="C6" s="6">
+        <f>33429+58692+64303</f>
+        <v>156424</v>
+      </c>
       <c r="D6" s="6"/>
       <c r="E6" s="6"/>
       <c r="F6" s="6"/>
@@ -3930,7 +4019,9 @@
       <c r="B7" s="6">
         <v>23696</v>
       </c>
-      <c r="C7" s="6"/>
+      <c r="C7" s="6">
+        <v>24185</v>
+      </c>
       <c r="D7" s="6"/>
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
@@ -3952,11 +4043,11 @@
         <v>161748</v>
       </c>
       <c r="C8" s="11">
-        <f t="shared" ref="C8:M8" si="1">SUM(C6:C7)</f>
-        <v>0</v>
+        <f>SUM(C6:C7)</f>
+        <v>180609</v>
       </c>
       <c r="D8" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="C8:M8" si="1">SUM(D6:D7)</f>
         <v>0</v>
       </c>
       <c r="E8" s="11">
@@ -4061,7 +4152,7 @@
       </c>
       <c r="C12" s="13">
         <f t="shared" ref="C12:M12" si="2">C8+C5</f>
-        <v>0</v>
+        <v>4932419</v>
       </c>
       <c r="D12" s="13">
         <f t="shared" si="2"/>
@@ -4115,7 +4206,7 @@
       </c>
       <c r="C13" s="13">
         <f t="shared" ref="C13:M13" si="3">C12-C11</f>
-        <v>0</v>
+        <v>4932419</v>
       </c>
       <c r="D13" s="13">
         <f t="shared" si="3"/>

--- a/article/家庭财务管理手册2026.xlsx
+++ b/article/家庭财务管理手册2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\baoyaoyao\Downloads\luyao.github.io-main\luyao.github.io-main\article\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\18717\Documents\GitHub\luyao.github.io\article\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20542B1F-ABFE-44A9-B959-CCED2AD5AEA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66A39172-7943-4755-BF8A-B364683F5C39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1、收入结余表" sheetId="2" r:id="rId1"/>
@@ -118,10 +118,6 @@
     <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
-    <t>南方</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
     <t>支付宝</t>
     <phoneticPr fontId="11" type="noConversion"/>
   </si>
@@ -187,6 +183,10 @@
   <si>
     <t>目标值</t>
     <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -390,7 +390,7 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -491,9 +491,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="176" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
@@ -633,7 +630,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'1、收入结余表'!$B$14</c:f>
+              <c:f>'1、收入结余表'!$B$13</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -992,7 +989,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'1、收入结余表'!$C$14:$I$14</c:f>
+              <c:f>'1、收入结余表'!$C$13:$I$13</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="7"/>
@@ -1175,10 +1172,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>'1、收入结余表'!$B$3:$B$13</c:f>
+              <c:f>'1、收入结余表'!$B$3:$B$12</c:f>
               <c:numCache>
                 <c:formatCode>m"月"</c:formatCode>
-                <c:ptCount val="11"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>44562</c:v>
                 </c:pt>
@@ -1186,30 +1183,27 @@
                   <c:v>44593</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>44652</c:v>
+                  <c:v>44682</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>44682</c:v>
+                  <c:v>44713</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>44713</c:v>
+                  <c:v>44743</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>44743</c:v>
+                  <c:v>44774</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>44774</c:v>
+                  <c:v>44805</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>44805</c:v>
+                  <c:v>44835</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>44835</c:v>
+                  <c:v>44866</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>44866</c:v>
-                </c:pt>
-                <c:pt idx="10">
                   <c:v>44896</c:v>
                 </c:pt>
               </c:numCache>
@@ -1217,10 +1211,10 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'1、收入结余表'!$N$3:$N$13</c:f>
+              <c:f>'1、收入结余表'!$N$3:$N$12</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
-                <c:ptCount val="11"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>5940295.1699999999</c:v>
                 </c:pt>
@@ -1228,7 +1222,7 @@
                   <c:v>7124085.7999999998</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>7516913.29</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>0</c:v>
@@ -1249,9 +1243,6 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="10">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -1469,13 +1460,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>19050</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>14</xdr:row>
       <xdr:rowOff>201241</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
       <xdr:colOff>20755</xdr:colOff>
-      <xdr:row>31</xdr:row>
+      <xdr:row>30</xdr:row>
       <xdr:rowOff>238125</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -1505,13 +1496,13 @@
     <xdr:from>
       <xdr:col>8</xdr:col>
       <xdr:colOff>38100</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>15</xdr:row>
       <xdr:rowOff>12163</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
       <xdr:colOff>285751</xdr:colOff>
-      <xdr:row>31</xdr:row>
+      <xdr:row>30</xdr:row>
       <xdr:rowOff>59114</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -2579,7 +2570,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:Q15"/>
+  <dimension ref="B1:Q14"/>
   <sheetFormatPr defaultColWidth="16.36328125" defaultRowHeight="19.899999999999999" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="2" style="1" customWidth="1"/>
@@ -2595,7 +2586,7 @@
     <row r="1" spans="2:17" ht="20.25" customHeight="1"/>
     <row r="2" spans="2:17" ht="25" customHeight="1">
       <c r="B2" s="16">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>1</v>
@@ -2633,11 +2624,11 @@
       <c r="N2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="O2" s="40" t="s">
-        <v>43</v>
+      <c r="O2" s="39" t="s">
+        <v>42</v>
       </c>
       <c r="P2" s="30" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="2:17" ht="24.65" customHeight="1">
@@ -2656,10 +2647,10 @@
       <c r="L3" s="25"/>
       <c r="M3" s="28"/>
       <c r="N3" s="25">
-        <f>'2、存量资产-y'!B26+'3、存量资产-k'!B13</f>
+        <f>'2、存量资产-y'!B25+'3、存量资产-k'!B13</f>
         <v>5940295.1699999999</v>
       </c>
-      <c r="O3" s="37">
+      <c r="O3" s="36">
         <v>6500000</v>
       </c>
       <c r="P3" s="31">
@@ -2683,10 +2674,10 @@
       <c r="L4" s="25"/>
       <c r="M4" s="28"/>
       <c r="N4" s="25">
-        <f>'2、存量资产-y'!C26+'3、存量资产-k'!C13</f>
+        <f>'2、存量资产-y'!C25+'3、存量资产-k'!C13</f>
         <v>7124085.7999999998</v>
       </c>
-      <c r="O4" s="37">
+      <c r="O4" s="36">
         <v>8000000</v>
       </c>
       <c r="P4" s="31">
@@ -2696,7 +2687,7 @@
     </row>
     <row r="5" spans="2:17" ht="24.65" customHeight="1">
       <c r="B5" s="17">
-        <v>44652</v>
+        <v>44682</v>
       </c>
       <c r="C5" s="18"/>
       <c r="D5" s="18"/>
@@ -2710,17 +2701,20 @@
       <c r="L5" s="25"/>
       <c r="M5" s="28"/>
       <c r="N5" s="25">
-        <f>'2、存量资产-y'!B28+'3、存量资产-k'!B15</f>
-        <v>0</v>
-      </c>
-      <c r="O5" s="37">
-        <v>6500000</v>
-      </c>
-      <c r="P5" s="31"/>
+        <f>'2、存量资产-y'!F25+'3、存量资产-k'!F13</f>
+        <v>7516913.29</v>
+      </c>
+      <c r="O5" s="36">
+        <v>8000000</v>
+      </c>
+      <c r="P5" s="31">
+        <f>N5/O5</f>
+        <v>0.93961416124999997</v>
+      </c>
     </row>
     <row r="6" spans="2:17" ht="24.65" customHeight="1">
       <c r="B6" s="17">
-        <v>44682</v>
+        <v>44713</v>
       </c>
       <c r="C6" s="18"/>
       <c r="D6" s="18"/>
@@ -2734,17 +2728,17 @@
       <c r="L6" s="25"/>
       <c r="M6" s="28"/>
       <c r="N6" s="25">
-        <f>'2、存量资产-y'!B29+'3、存量资产-k'!B16</f>
-        <v>0</v>
-      </c>
-      <c r="O6" s="37">
-        <v>6500000</v>
+        <f>'2、存量资产-y'!B29+'3、存量资产-k'!B17</f>
+        <v>0</v>
+      </c>
+      <c r="O6" s="36">
+        <v>8000000</v>
       </c>
       <c r="P6" s="31"/>
     </row>
     <row r="7" spans="2:17" ht="24.65" customHeight="1">
       <c r="B7" s="17">
-        <v>44713</v>
+        <v>44743</v>
       </c>
       <c r="C7" s="18"/>
       <c r="D7" s="18"/>
@@ -2758,17 +2752,17 @@
       <c r="L7" s="25"/>
       <c r="M7" s="28"/>
       <c r="N7" s="25">
-        <f>'2、存量资产-y'!B30+'3、存量资产-k'!B17</f>
-        <v>0</v>
-      </c>
-      <c r="O7" s="37">
-        <v>6500000</v>
+        <f>'2、存量资产-y'!B30+'3、存量资产-k'!B18</f>
+        <v>0</v>
+      </c>
+      <c r="O7" s="36">
+        <v>8000000</v>
       </c>
       <c r="P7" s="31"/>
     </row>
     <row r="8" spans="2:17" ht="24.65" customHeight="1">
       <c r="B8" s="17">
-        <v>44743</v>
+        <v>44774</v>
       </c>
       <c r="C8" s="18"/>
       <c r="D8" s="18"/>
@@ -2782,17 +2776,15 @@
       <c r="L8" s="25"/>
       <c r="M8" s="28"/>
       <c r="N8" s="25">
-        <f>'2、存量资产-y'!B31+'3、存量资产-k'!B18</f>
-        <v>0</v>
-      </c>
-      <c r="O8" s="37">
-        <v>6500000</v>
-      </c>
+        <f>'2、存量资产-y'!B31+'3、存量资产-k'!B19</f>
+        <v>0</v>
+      </c>
+      <c r="O8" s="36"/>
       <c r="P8" s="31"/>
     </row>
     <row r="9" spans="2:17" ht="24.65" customHeight="1">
       <c r="B9" s="17">
-        <v>44774</v>
+        <v>44805</v>
       </c>
       <c r="C9" s="18"/>
       <c r="D9" s="18"/>
@@ -2806,15 +2798,16 @@
       <c r="L9" s="25"/>
       <c r="M9" s="28"/>
       <c r="N9" s="25">
-        <f>'2、存量资产-y'!B32+'3、存量资产-k'!B19</f>
-        <v>0</v>
-      </c>
-      <c r="O9" s="37"/>
+        <f>'2、存量资产-y'!B32+'3、存量资产-k'!B20</f>
+        <v>0</v>
+      </c>
+      <c r="O9" s="36"/>
       <c r="P9" s="31"/>
+      <c r="Q9" s="34"/>
     </row>
     <row r="10" spans="2:17" ht="24.65" customHeight="1">
       <c r="B10" s="17">
-        <v>44805</v>
+        <v>44835</v>
       </c>
       <c r="C10" s="18"/>
       <c r="D10" s="18"/>
@@ -2828,16 +2821,15 @@
       <c r="L10" s="25"/>
       <c r="M10" s="28"/>
       <c r="N10" s="25">
-        <f>'2、存量资产-y'!B33+'3、存量资产-k'!B20</f>
-        <v>0</v>
-      </c>
-      <c r="O10" s="37"/>
+        <f>'2、存量资产-y'!B33+'3、存量资产-k'!B21</f>
+        <v>0</v>
+      </c>
+      <c r="O10" s="36"/>
       <c r="P10" s="31"/>
-      <c r="Q10" s="35"/>
     </row>
     <row r="11" spans="2:17" ht="24.65" customHeight="1">
       <c r="B11" s="17">
-        <v>44835</v>
+        <v>44866</v>
       </c>
       <c r="C11" s="18"/>
       <c r="D11" s="18"/>
@@ -2851,15 +2843,15 @@
       <c r="L11" s="25"/>
       <c r="M11" s="28"/>
       <c r="N11" s="25">
-        <f>'2、存量资产-y'!B34+'3、存量资产-k'!B21</f>
-        <v>0</v>
-      </c>
-      <c r="O11" s="37"/>
+        <f>'2、存量资产-y'!B34+'3、存量资产-k'!B22</f>
+        <v>0</v>
+      </c>
+      <c r="O11" s="36"/>
       <c r="P11" s="31"/>
     </row>
     <row r="12" spans="2:17" ht="24.65" customHeight="1">
       <c r="B12" s="17">
-        <v>44866</v>
+        <v>44896</v>
       </c>
       <c r="C12" s="18"/>
       <c r="D12" s="18"/>
@@ -2873,131 +2865,109 @@
       <c r="L12" s="25"/>
       <c r="M12" s="28"/>
       <c r="N12" s="25">
-        <f>'2、存量资产-y'!B35+'3、存量资产-k'!B22</f>
-        <v>0</v>
-      </c>
-      <c r="O12" s="37"/>
+        <f>'2、存量资产-y'!B35+'3、存量资产-k'!B23</f>
+        <v>0</v>
+      </c>
+      <c r="O12" s="36"/>
       <c r="P12" s="31"/>
     </row>
-    <row r="13" spans="2:17" ht="24.65" customHeight="1">
-      <c r="B13" s="17">
-        <v>44896</v>
-      </c>
-      <c r="C13" s="18"/>
-      <c r="D13" s="18"/>
-      <c r="E13" s="18"/>
-      <c r="F13" s="18"/>
-      <c r="G13" s="18"/>
-      <c r="H13" s="18"/>
-      <c r="I13" s="18"/>
-      <c r="J13" s="18"/>
-      <c r="K13" s="24"/>
-      <c r="L13" s="25"/>
-      <c r="M13" s="28"/>
-      <c r="N13" s="25">
-        <f>'2、存量资产-y'!B36+'3、存量资产-k'!B23</f>
-        <v>0</v>
-      </c>
+    <row r="13" spans="2:17" ht="25" customHeight="1">
+      <c r="B13" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="C13" s="20">
+        <f>SUM(C3:C12)</f>
+        <v>0</v>
+      </c>
+      <c r="D13" s="20">
+        <f>SUM(D3:D12)</f>
+        <v>0</v>
+      </c>
+      <c r="E13" s="20">
+        <f>SUM(E3:E12)</f>
+        <v>0</v>
+      </c>
+      <c r="F13" s="20">
+        <f>SUM(F3:F12)</f>
+        <v>0</v>
+      </c>
+      <c r="G13" s="20">
+        <f>SUM(G3:G12)</f>
+        <v>0</v>
+      </c>
+      <c r="H13" s="20">
+        <f>SUM(H3:H12)</f>
+        <v>0</v>
+      </c>
+      <c r="I13" s="20">
+        <f>SUM(I3:I12)</f>
+        <v>0</v>
+      </c>
+      <c r="J13" s="20">
+        <f>SUM(J3:J12)</f>
+        <v>0</v>
+      </c>
+      <c r="K13" s="26">
+        <f>SUM(K3:K12)</f>
+        <v>0</v>
+      </c>
+      <c r="L13" s="27">
+        <f>SUM(L3:L12)</f>
+        <v>0</v>
+      </c>
+      <c r="M13" s="29" t="e">
+        <f t="shared" ref="M13" si="0">L13/J13</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N13" s="27"/>
       <c r="O13" s="37"/>
       <c r="P13" s="31"/>
     </row>
     <row r="14" spans="2:17" ht="25" customHeight="1">
-      <c r="B14" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="C14" s="20">
-        <f t="shared" ref="C14:L14" si="0">SUM(C3:C13)</f>
-        <v>0</v>
-      </c>
-      <c r="D14" s="20">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="E14" s="20">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F14" s="20">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G14" s="20">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H14" s="20">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I14" s="20">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J14" s="20">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K14" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="L14" s="27">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="M14" s="29" t="e">
-        <f t="shared" ref="M14" si="1">L14/J14</f>
+      <c r="B14" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="C14" s="22" t="e">
+        <f t="shared" ref="C14:J14" si="1">C13/$J13</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="N14" s="27"/>
+      <c r="D14" s="22" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E14" s="22" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F14" s="22" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G14" s="22" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H14" s="22" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I14" s="22" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J14" s="22" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K14" s="22"/>
+      <c r="L14" s="22"/>
+      <c r="M14" s="22" t="e">
+        <f>N13/J13</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N14" s="22"/>
       <c r="O14" s="38"/>
       <c r="P14" s="31"/>
-    </row>
-    <row r="15" spans="2:17" ht="25" customHeight="1">
-      <c r="B15" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="C15" s="22" t="e">
-        <f t="shared" ref="C15:J15" si="2">C14/$J14</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="D15" s="22" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E15" s="22" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F15" s="22" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G15" s="22" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H15" s="22" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I15" s="22" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J15" s="22" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K15" s="22"/>
-      <c r="L15" s="22"/>
-      <c r="M15" s="22" t="e">
-        <f>N14/J14</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N15" s="22"/>
-      <c r="O15" s="39"/>
-      <c r="P15" s="31"/>
     </row>
   </sheetData>
   <phoneticPr fontId="10" type="noConversion"/>
@@ -3015,7 +2985,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N26"/>
+  <dimension ref="A1:N25"/>
   <sheetFormatPr defaultColWidth="16.36328125" defaultRowHeight="19.899999999999999" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="14.453125" style="1" customWidth="1"/>
@@ -3026,7 +2996,7 @@
   <sheetData>
     <row r="1" spans="1:14" ht="21.65" customHeight="1">
       <c r="A1" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B1" s="4">
         <v>2026.1</v>
@@ -3077,7 +3047,9 @@
       </c>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
+      <c r="F2" s="6">
+        <v>11830.94</v>
+      </c>
       <c r="G2" s="32"/>
       <c r="H2" s="6"/>
       <c r="I2" s="6"/>
@@ -3099,7 +3071,9 @@
       </c>
       <c r="D3" s="7"/>
       <c r="E3" s="7"/>
-      <c r="F3" s="7"/>
+      <c r="F3" s="7">
+        <v>136231.75</v>
+      </c>
       <c r="G3" s="32"/>
       <c r="H3" s="6"/>
       <c r="I3" s="7"/>
@@ -3119,7 +3093,9 @@
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
-      <c r="F4" s="6"/>
+      <c r="F4" s="6">
+        <v>285165.96000000002</v>
+      </c>
       <c r="G4" s="33"/>
       <c r="H4" s="6"/>
       <c r="I4" s="6"/>
@@ -3141,7 +3117,9 @@
       </c>
       <c r="D5" s="7"/>
       <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
+      <c r="F5" s="7">
+        <v>0</v>
+      </c>
       <c r="G5" s="6"/>
       <c r="H5" s="6"/>
       <c r="I5" s="7"/>
@@ -3163,7 +3141,9 @@
       </c>
       <c r="D6" s="6"/>
       <c r="E6" s="6"/>
-      <c r="F6" s="6"/>
+      <c r="F6" s="6">
+        <v>225255</v>
+      </c>
       <c r="G6" s="6"/>
       <c r="H6" s="6"/>
       <c r="I6" s="6"/>
@@ -3178,34 +3158,36 @@
         <v>25</v>
       </c>
       <c r="B7" s="6">
-        <v>0</v>
-      </c>
-      <c r="C7" s="6"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
+        <v>32475.64</v>
+      </c>
+      <c r="C7" s="6">
+        <v>32682</v>
+      </c>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6">
+        <v>29456.53</v>
+      </c>
       <c r="G7" s="6"/>
       <c r="H7" s="6"/>
-      <c r="I7" s="7"/>
-      <c r="J7" s="34"/>
-      <c r="K7" s="7"/>
-      <c r="L7" s="7"/>
-      <c r="M7" s="7"/>
+      <c r="I7" s="6"/>
+      <c r="J7" s="6"/>
+      <c r="K7" s="6"/>
+      <c r="L7" s="6"/>
+      <c r="M7" s="6"/>
       <c r="N7" s="15"/>
     </row>
     <row r="8" spans="1:14" ht="20.5" customHeight="1">
       <c r="A8" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="B8" s="6">
-        <v>32475.64</v>
-      </c>
-      <c r="C8" s="6">
-        <v>32682</v>
-      </c>
+      <c r="B8" s="6"/>
+      <c r="C8" s="6"/>
       <c r="D8" s="6"/>
       <c r="E8" s="6"/>
-      <c r="F8" s="6"/>
+      <c r="F8" s="6">
+        <v>1471</v>
+      </c>
       <c r="G8" s="6"/>
       <c r="H8" s="6"/>
       <c r="I8" s="6"/>
@@ -3219,11 +3201,17 @@
       <c r="A9" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="B9" s="6"/>
-      <c r="C9" s="6"/>
+      <c r="B9" s="6">
+        <v>10749</v>
+      </c>
+      <c r="C9" s="6">
+        <v>17075</v>
+      </c>
       <c r="D9" s="6"/>
       <c r="E9" s="6"/>
-      <c r="F9" s="6"/>
+      <c r="F9" s="6">
+        <v>0</v>
+      </c>
       <c r="G9" s="6"/>
       <c r="H9" s="6"/>
       <c r="I9" s="6"/>
@@ -3235,24 +3223,44 @@
     </row>
     <row r="10" spans="1:14" ht="20.5" customHeight="1">
       <c r="A10" s="5" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="B10" s="6">
-        <v>10749</v>
+        <v>500000</v>
       </c>
       <c r="C10" s="6">
-        <v>17075</v>
-      </c>
-      <c r="D10" s="6"/>
-      <c r="E10" s="6"/>
-      <c r="F10" s="6"/>
-      <c r="G10" s="6"/>
-      <c r="H10" s="6"/>
-      <c r="I10" s="6"/>
-      <c r="J10" s="6"/>
-      <c r="K10" s="6"/>
-      <c r="L10" s="6"/>
-      <c r="M10" s="6"/>
+        <v>500000</v>
+      </c>
+      <c r="D10" s="6">
+        <v>500000</v>
+      </c>
+      <c r="E10" s="6">
+        <v>500000</v>
+      </c>
+      <c r="F10" s="6">
+        <v>500000</v>
+      </c>
+      <c r="G10" s="6">
+        <v>500000</v>
+      </c>
+      <c r="H10" s="6">
+        <v>500000</v>
+      </c>
+      <c r="I10" s="6">
+        <v>500000</v>
+      </c>
+      <c r="J10" s="6">
+        <v>500000</v>
+      </c>
+      <c r="K10" s="6">
+        <v>500000</v>
+      </c>
+      <c r="L10" s="6">
+        <v>500000</v>
+      </c>
+      <c r="M10" s="6">
+        <v>500000</v>
+      </c>
       <c r="N10" s="15"/>
     </row>
     <row r="11" spans="1:14" ht="20.5" customHeight="1">
@@ -3299,44 +3307,26 @@
     </row>
     <row r="12" spans="1:14" ht="20.5" customHeight="1">
       <c r="A12" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B12" s="6">
-        <v>500000</v>
+        <v>19988.490000000002</v>
       </c>
       <c r="C12" s="6">
-        <v>500000</v>
-      </c>
-      <c r="D12" s="6">
-        <v>500000</v>
-      </c>
-      <c r="E12" s="6">
-        <v>500000</v>
-      </c>
+        <v>19935</v>
+      </c>
+      <c r="D12" s="6"/>
+      <c r="E12" s="6"/>
       <c r="F12" s="6">
-        <v>500000</v>
-      </c>
-      <c r="G12" s="6">
-        <v>500000</v>
-      </c>
-      <c r="H12" s="6">
-        <v>500000</v>
-      </c>
-      <c r="I12" s="6">
-        <v>500000</v>
-      </c>
-      <c r="J12" s="6">
-        <v>500000</v>
-      </c>
-      <c r="K12" s="6">
-        <v>500000</v>
-      </c>
-      <c r="L12" s="6">
-        <v>500000</v>
-      </c>
-      <c r="M12" s="6">
-        <v>500000</v>
-      </c>
+        <v>19547.27</v>
+      </c>
+      <c r="G12" s="6"/>
+      <c r="H12" s="6"/>
+      <c r="I12" s="6"/>
+      <c r="J12" s="7"/>
+      <c r="K12" s="6"/>
+      <c r="L12" s="6"/>
+      <c r="M12" s="6"/>
       <c r="N12" s="15"/>
     </row>
     <row r="13" spans="1:14" ht="20.5" customHeight="1">
@@ -3344,18 +3334,20 @@
         <v>38</v>
       </c>
       <c r="B13" s="6">
-        <v>19988.490000000002</v>
+        <v>368986.86</v>
       </c>
       <c r="C13" s="6">
-        <v>19935</v>
+        <v>367684</v>
       </c>
       <c r="D13" s="6"/>
       <c r="E13" s="6"/>
-      <c r="F13" s="6"/>
+      <c r="F13" s="6">
+        <v>361890.96</v>
+      </c>
       <c r="G13" s="6"/>
       <c r="H13" s="6"/>
       <c r="I13" s="6"/>
-      <c r="J13" s="7"/>
+      <c r="J13" s="6"/>
       <c r="K13" s="6"/>
       <c r="L13" s="6"/>
       <c r="M13" s="6"/>
@@ -3366,14 +3358,16 @@
         <v>39</v>
       </c>
       <c r="B14" s="6">
-        <v>368986.86</v>
+        <v>32279</v>
       </c>
       <c r="C14" s="6">
-        <v>367684</v>
+        <v>32226</v>
       </c>
       <c r="D14" s="6"/>
       <c r="E14" s="6"/>
-      <c r="F14" s="6"/>
+      <c r="F14" s="6">
+        <v>31462</v>
+      </c>
       <c r="G14" s="6"/>
       <c r="H14" s="6"/>
       <c r="I14" s="6"/>
@@ -3388,14 +3382,16 @@
         <v>40</v>
       </c>
       <c r="B15" s="6">
-        <v>32279</v>
+        <v>102080</v>
       </c>
       <c r="C15" s="6">
-        <v>32226</v>
+        <v>101693</v>
       </c>
       <c r="D15" s="6"/>
       <c r="E15" s="6"/>
-      <c r="F15" s="6"/>
+      <c r="F15" s="6">
+        <v>99885.88</v>
+      </c>
       <c r="G15" s="6"/>
       <c r="H15" s="6"/>
       <c r="I15" s="6"/>
@@ -3406,94 +3402,98 @@
       <c r="N15" s="15"/>
     </row>
     <row r="16" spans="1:14" ht="20.5" customHeight="1">
-      <c r="A16" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B16" s="6">
-        <v>102080</v>
-      </c>
-      <c r="C16" s="6">
-        <v>101693</v>
-      </c>
-      <c r="D16" s="6"/>
-      <c r="E16" s="6"/>
-      <c r="F16" s="6"/>
-      <c r="G16" s="6"/>
-      <c r="H16" s="6"/>
-      <c r="I16" s="6"/>
-      <c r="J16" s="6"/>
-      <c r="K16" s="6"/>
-      <c r="L16" s="6"/>
-      <c r="M16" s="6"/>
+      <c r="A16" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B16" s="9">
+        <f>SUM(B2:B15)</f>
+        <v>1846341.17</v>
+      </c>
+      <c r="C16" s="9">
+        <f>SUM(C2:C15)</f>
+        <v>1896189.8</v>
+      </c>
+      <c r="D16" s="9">
+        <f>SUM(D2:D15)</f>
+        <v>1000000</v>
+      </c>
+      <c r="E16" s="9">
+        <f>SUM(E2:E15)</f>
+        <v>1000000</v>
+      </c>
+      <c r="F16" s="9">
+        <f>SUM(F2:F15)</f>
+        <v>2202197.29</v>
+      </c>
+      <c r="G16" s="9">
+        <f>SUM(G2:G15)</f>
+        <v>1000000</v>
+      </c>
+      <c r="H16" s="9">
+        <f>SUM(H2:H15)</f>
+        <v>1000000</v>
+      </c>
+      <c r="I16" s="9">
+        <f>SUM(I2:I15)</f>
+        <v>1000000</v>
+      </c>
+      <c r="J16" s="9">
+        <f>SUM(J2:J15)</f>
+        <v>1000000</v>
+      </c>
+      <c r="K16" s="9">
+        <f>SUM(K2:K15)</f>
+        <v>1000000</v>
+      </c>
+      <c r="L16" s="9">
+        <f>SUM(L2:L15)</f>
+        <v>1000000</v>
+      </c>
+      <c r="M16" s="9">
+        <f>SUM(M2:M15)</f>
+        <v>1000000</v>
+      </c>
       <c r="N16" s="15"/>
     </row>
     <row r="17" spans="1:14" ht="20.5" customHeight="1">
-      <c r="A17" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="B17" s="9">
-        <f>SUM(B2:B16)</f>
-        <v>1846341.17</v>
-      </c>
-      <c r="C17" s="9">
-        <f t="shared" ref="C17:M17" si="0">SUM(C2:C16)</f>
-        <v>1896189.8</v>
-      </c>
-      <c r="D17" s="9">
-        <f t="shared" si="0"/>
-        <v>1000000</v>
-      </c>
-      <c r="E17" s="9">
-        <f t="shared" si="0"/>
-        <v>1000000</v>
-      </c>
-      <c r="F17" s="9">
-        <f t="shared" si="0"/>
-        <v>1000000</v>
-      </c>
-      <c r="G17" s="9">
-        <f t="shared" si="0"/>
-        <v>1000000</v>
-      </c>
-      <c r="H17" s="9">
-        <f t="shared" si="0"/>
-        <v>1000000</v>
-      </c>
-      <c r="I17" s="9">
-        <f t="shared" si="0"/>
-        <v>1000000</v>
-      </c>
-      <c r="J17" s="9">
-        <f t="shared" si="0"/>
-        <v>1000000</v>
-      </c>
-      <c r="K17" s="9">
-        <f t="shared" si="0"/>
-        <v>1000000</v>
-      </c>
-      <c r="L17" s="9">
-        <f t="shared" si="0"/>
-        <v>1000000</v>
-      </c>
-      <c r="M17" s="9">
-        <f t="shared" si="0"/>
-        <v>1000000</v>
-      </c>
+      <c r="A17" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17" s="6">
+        <v>135584</v>
+      </c>
+      <c r="C17" s="6">
+        <v>135731</v>
+      </c>
+      <c r="D17" s="6"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="6">
+        <v>136319</v>
+      </c>
+      <c r="G17" s="6"/>
+      <c r="H17" s="6"/>
+      <c r="I17" s="6"/>
+      <c r="J17" s="6"/>
+      <c r="K17" s="6"/>
+      <c r="L17" s="6"/>
+      <c r="M17" s="6"/>
       <c r="N17" s="15"/>
     </row>
     <row r="18" spans="1:14" ht="20.5" customHeight="1">
       <c r="A18" s="5" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="B18" s="6">
-        <v>135584</v>
+        <v>133109</v>
       </c>
       <c r="C18" s="6">
-        <v>135731</v>
+        <v>136839</v>
       </c>
       <c r="D18" s="6"/>
       <c r="E18" s="6"/>
-      <c r="F18" s="6"/>
+      <c r="F18" s="6">
+        <v>151759</v>
+      </c>
       <c r="G18" s="6"/>
       <c r="H18" s="6"/>
       <c r="I18" s="6"/>
@@ -3508,199 +3508,235 @@
         <v>29</v>
       </c>
       <c r="B19" s="6">
-        <v>133109</v>
+        <v>22604</v>
       </c>
       <c r="C19" s="6">
-        <v>136839</v>
-      </c>
-      <c r="D19" s="6"/>
-      <c r="E19" s="6"/>
-      <c r="F19" s="6"/>
-      <c r="G19" s="6"/>
-      <c r="H19" s="6"/>
-      <c r="I19" s="6"/>
-      <c r="J19" s="6"/>
-      <c r="K19" s="6"/>
-      <c r="L19" s="6"/>
-      <c r="M19" s="6"/>
+        <v>22907</v>
+      </c>
+      <c r="D19" s="7"/>
+      <c r="E19" s="7"/>
+      <c r="F19" s="7">
+        <v>22810</v>
+      </c>
+      <c r="G19" s="7"/>
+      <c r="H19" s="7"/>
+      <c r="I19" s="7"/>
+      <c r="J19" s="7"/>
+      <c r="K19" s="7"/>
+      <c r="L19" s="7"/>
+      <c r="M19" s="7"/>
       <c r="N19" s="15"/>
     </row>
     <row r="20" spans="1:14" ht="20.5" customHeight="1">
-      <c r="A20" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="B20" s="6">
-        <v>22604</v>
-      </c>
-      <c r="C20" s="6">
-        <v>22907</v>
-      </c>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="7"/>
-      <c r="G20" s="7"/>
-      <c r="H20" s="7"/>
-      <c r="I20" s="7"/>
-      <c r="J20" s="7"/>
-      <c r="K20" s="7"/>
-      <c r="L20" s="7"/>
-      <c r="M20" s="7"/>
+      <c r="A20" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B20" s="11">
+        <f>SUM(B17:B19)</f>
+        <v>291297</v>
+      </c>
+      <c r="C20" s="11">
+        <f t="shared" ref="C20:M20" si="0">SUM(C17:C19)</f>
+        <v>295477</v>
+      </c>
+      <c r="D20" s="11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E20" s="11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F20" s="11">
+        <f>SUM(F17:F19)</f>
+        <v>310888</v>
+      </c>
+      <c r="G20" s="11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H20" s="11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I20" s="11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J20" s="11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K20" s="11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L20" s="11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="M20" s="11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="N20" s="15"/>
     </row>
     <row r="21" spans="1:14" ht="20.5" customHeight="1">
-      <c r="A21" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="B21" s="11">
-        <f>SUM(B18:B20)</f>
-        <v>291297</v>
-      </c>
-      <c r="C21" s="11">
-        <f t="shared" ref="C21:M21" si="1">SUM(C18:C20)</f>
-        <v>295477</v>
-      </c>
-      <c r="D21" s="11">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="E21" s="11">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="F21" s="11">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G21" s="11">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H21" s="11">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I21" s="11">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J21" s="11">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K21" s="11">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L21" s="11">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="M21" s="11">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="A21" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B21" s="7"/>
+      <c r="C21" s="7"/>
+      <c r="D21" s="7"/>
+      <c r="E21" s="7"/>
+      <c r="F21" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="G21" s="7"/>
+      <c r="H21" s="7"/>
+      <c r="I21" s="7"/>
+      <c r="J21" s="7"/>
+      <c r="K21" s="7"/>
+      <c r="L21" s="7"/>
+      <c r="M21" s="7"/>
       <c r="N21" s="15"/>
     </row>
     <row r="22" spans="1:14" ht="20.5" customHeight="1">
       <c r="A22" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B22" s="7"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="7"/>
-      <c r="G22" s="7"/>
-      <c r="H22" s="7"/>
-      <c r="I22" s="7"/>
-      <c r="J22" s="7"/>
-      <c r="K22" s="7"/>
-      <c r="L22" s="7"/>
-      <c r="M22" s="7"/>
+        <v>16</v>
+      </c>
+      <c r="B22" s="6"/>
+      <c r="C22" s="6"/>
+      <c r="D22" s="6"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="6"/>
+      <c r="G22" s="6"/>
+      <c r="H22" s="6"/>
+      <c r="I22" s="6"/>
+      <c r="J22" s="6"/>
+      <c r="K22" s="6"/>
+      <c r="L22" s="6"/>
+      <c r="M22" s="6"/>
       <c r="N22" s="15"/>
     </row>
     <row r="23" spans="1:14" ht="20.5" customHeight="1">
-      <c r="A23" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B23" s="6"/>
-      <c r="C23" s="6"/>
-      <c r="D23" s="6"/>
-      <c r="E23" s="6"/>
-      <c r="F23" s="6"/>
-      <c r="G23" s="6"/>
-      <c r="H23" s="6"/>
-      <c r="I23" s="6"/>
-      <c r="J23" s="6"/>
-      <c r="K23" s="6"/>
-      <c r="L23" s="6"/>
-      <c r="M23" s="6"/>
+      <c r="A23" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B23" s="9">
+        <f>SUM(B21:B22)</f>
+        <v>0</v>
+      </c>
+      <c r="C23" s="9">
+        <f t="shared" ref="C23:M23" si="1">SUM(C21:C22)</f>
+        <v>0</v>
+      </c>
+      <c r="D23" s="9">
+        <f>SUM(D21:D22)</f>
+        <v>0</v>
+      </c>
+      <c r="E23" s="9">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F23" s="9">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G23" s="9">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H23" s="9">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I23" s="9">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J23" s="9">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K23" s="9">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L23" s="9">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M23" s="9">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="N23" s="15"/>
     </row>
-    <row r="24" spans="1:14" ht="20.5" customHeight="1">
-      <c r="A24" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="B24" s="9">
-        <f>SUM(B22:B23)</f>
-        <v>0</v>
-      </c>
-      <c r="C24" s="9">
-        <f t="shared" ref="C24:M24" si="2">SUM(C22:C23)</f>
-        <v>0</v>
-      </c>
-      <c r="D24" s="9">
-        <f>SUM(D22:D23)</f>
-        <v>0</v>
-      </c>
-      <c r="E24" s="9">
+    <row r="24" spans="1:14" ht="19.899999999999999" customHeight="1">
+      <c r="A24" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="B24" s="13">
+        <f>SUM(B16,B20)</f>
+        <v>2137638.17</v>
+      </c>
+      <c r="C24" s="13">
+        <f t="shared" ref="C24:M24" si="2">SUM(C16,C20)</f>
+        <v>2191666.7999999998</v>
+      </c>
+      <c r="D24" s="13">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F24" s="9">
+        <v>1000000</v>
+      </c>
+      <c r="E24" s="13">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G24" s="9">
+        <v>1000000</v>
+      </c>
+      <c r="F24" s="13">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H24" s="9">
+        <v>2513085.29</v>
+      </c>
+      <c r="G24" s="13">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I24" s="9">
+        <v>1000000</v>
+      </c>
+      <c r="H24" s="13">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="J24" s="9">
+        <v>1000000</v>
+      </c>
+      <c r="I24" s="13">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K24" s="9">
+        <v>1000000</v>
+      </c>
+      <c r="J24" s="13">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="L24" s="9">
+        <v>1000000</v>
+      </c>
+      <c r="K24" s="13">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="M24" s="9">
+        <v>1000000</v>
+      </c>
+      <c r="L24" s="13">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1000000</v>
+      </c>
+      <c r="M24" s="13">
+        <f t="shared" si="2"/>
+        <v>1000000</v>
       </c>
       <c r="N24" s="15"/>
     </row>
     <row r="25" spans="1:14" ht="19.899999999999999" customHeight="1">
       <c r="A25" s="12" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B25" s="13">
-        <f>SUM(B17,B21)</f>
+        <f>B24-B23</f>
         <v>2137638.17</v>
       </c>
       <c r="C25" s="13">
-        <f t="shared" ref="C25:M25" si="3">SUM(C17,C21)</f>
+        <f t="shared" ref="C25:M25" si="3">C24-C23</f>
         <v>2191666.7999999998</v>
       </c>
       <c r="D25" s="13">
@@ -3713,7 +3749,7 @@
       </c>
       <c r="F25" s="13">
         <f t="shared" si="3"/>
-        <v>1000000</v>
+        <v>2513085.29</v>
       </c>
       <c r="G25" s="13">
         <f t="shared" si="3"/>
@@ -3744,60 +3780,6 @@
         <v>1000000</v>
       </c>
       <c r="N25" s="15"/>
-    </row>
-    <row r="26" spans="1:14" ht="19.899999999999999" customHeight="1">
-      <c r="A26" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="B26" s="13">
-        <f>B25-B24</f>
-        <v>2137638.17</v>
-      </c>
-      <c r="C26" s="13">
-        <f t="shared" ref="C26:M26" si="4">C25-C24</f>
-        <v>2191666.7999999998</v>
-      </c>
-      <c r="D26" s="13">
-        <f t="shared" si="4"/>
-        <v>1000000</v>
-      </c>
-      <c r="E26" s="13">
-        <f t="shared" si="4"/>
-        <v>1000000</v>
-      </c>
-      <c r="F26" s="13">
-        <f t="shared" si="4"/>
-        <v>1000000</v>
-      </c>
-      <c r="G26" s="13">
-        <f t="shared" si="4"/>
-        <v>1000000</v>
-      </c>
-      <c r="H26" s="13">
-        <f t="shared" si="4"/>
-        <v>1000000</v>
-      </c>
-      <c r="I26" s="13">
-        <f t="shared" si="4"/>
-        <v>1000000</v>
-      </c>
-      <c r="J26" s="13">
-        <f t="shared" si="4"/>
-        <v>1000000</v>
-      </c>
-      <c r="K26" s="13">
-        <f t="shared" si="4"/>
-        <v>1000000</v>
-      </c>
-      <c r="L26" s="13">
-        <f t="shared" si="4"/>
-        <v>1000000</v>
-      </c>
-      <c r="M26" s="13">
-        <f t="shared" si="4"/>
-        <v>1000000</v>
-      </c>
-      <c r="N26" s="15"/>
     </row>
   </sheetData>
   <phoneticPr fontId="11" type="noConversion"/>
@@ -3825,7 +3807,7 @@
   <sheetData>
     <row r="1" spans="1:14" ht="21.65" customHeight="1">
       <c r="A1" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B1" s="4">
         <v>2026.1</v>
@@ -3865,8 +3847,8 @@
       </c>
     </row>
     <row r="2" spans="1:14" ht="20.5" customHeight="1">
-      <c r="A2" s="36" t="s">
-        <v>42</v>
+      <c r="A2" s="35" t="s">
+        <v>41</v>
       </c>
       <c r="B2" s="6">
         <f>490768*7</f>
@@ -3878,7 +3860,10 @@
       </c>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
+      <c r="F2" s="6">
+        <f>602516*7</f>
+        <v>4217612</v>
+      </c>
       <c r="G2" s="6"/>
       <c r="H2" s="6"/>
       <c r="I2" s="6"/>
@@ -3890,7 +3875,7 @@
     </row>
     <row r="3" spans="1:14" ht="20.5" customHeight="1">
       <c r="A3" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B3" s="6">
         <f>155000+43677+1565+1234+307</f>
@@ -3902,7 +3887,9 @@
       </c>
       <c r="D3" s="7"/>
       <c r="E3" s="7"/>
-      <c r="F3" s="7"/>
+      <c r="F3" s="7">
+        <v>626003</v>
+      </c>
       <c r="G3" s="7"/>
       <c r="H3" s="7"/>
       <c r="I3" s="7"/>
@@ -3914,7 +3901,7 @@
     </row>
     <row r="4" spans="1:14" ht="20.5" customHeight="1">
       <c r="A4" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B4" s="6">
         <v>3750</v>
@@ -3924,7 +3911,10 @@
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
-      <c r="F4" s="6"/>
+      <c r="F4" s="6">
+        <f>15023+3705</f>
+        <v>18728</v>
+      </c>
       <c r="G4" s="6"/>
       <c r="H4" s="6"/>
       <c r="I4" s="6"/>
@@ -3956,7 +3946,7 @@
       </c>
       <c r="F5" s="9">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>4862343</v>
       </c>
       <c r="G5" s="9">
         <f t="shared" si="0"/>
@@ -4002,7 +3992,10 @@
       </c>
       <c r="D6" s="6"/>
       <c r="E6" s="6"/>
-      <c r="F6" s="6"/>
+      <c r="F6" s="6">
+        <f>23429+58692+35826</f>
+        <v>117947</v>
+      </c>
       <c r="G6" s="6"/>
       <c r="H6" s="6"/>
       <c r="I6" s="6"/>
@@ -4014,7 +4007,7 @@
     </row>
     <row r="7" spans="1:14" ht="20.5" customHeight="1">
       <c r="A7" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B7" s="6">
         <v>23696</v>
@@ -4024,7 +4017,9 @@
       </c>
       <c r="D7" s="6"/>
       <c r="E7" s="6"/>
-      <c r="F7" s="6"/>
+      <c r="F7" s="6">
+        <v>23538</v>
+      </c>
       <c r="G7" s="6"/>
       <c r="H7" s="6"/>
       <c r="I7" s="6"/>
@@ -4047,7 +4042,7 @@
         <v>180609</v>
       </c>
       <c r="D8" s="11">
-        <f t="shared" ref="C8:M8" si="1">SUM(D6:D7)</f>
+        <f t="shared" ref="D8:M8" si="1">SUM(D6:D7)</f>
         <v>0</v>
       </c>
       <c r="E8" s="11">
@@ -4056,7 +4051,7 @@
       </c>
       <c r="F8" s="11">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>141485</v>
       </c>
       <c r="G8" s="11">
         <f t="shared" si="1"/>
@@ -4164,7 +4159,7 @@
       </c>
       <c r="F12" s="13">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>5003828</v>
       </c>
       <c r="G12" s="13">
         <f t="shared" si="2"/>
@@ -4218,7 +4213,7 @@
       </c>
       <c r="F13" s="13">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>5003828</v>
       </c>
       <c r="G13" s="13">
         <f t="shared" si="3"/>

--- a/article/家庭财务管理手册2026.xlsx
+++ b/article/家庭财务管理手册2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\18717\Documents\GitHub\luyao.github.io\article\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66A39172-7943-4755-BF8A-B364683F5C39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{588D2197-D161-4FAD-A8BB-735D679547D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1225,10 +1225,7 @@
                   <c:v>7516913.29</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>8012723.4869999997</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>0</c:v>
@@ -2728,13 +2725,16 @@
       <c r="L6" s="25"/>
       <c r="M6" s="28"/>
       <c r="N6" s="25">
-        <f>'2、存量资产-y'!B29+'3、存量资产-k'!B17</f>
-        <v>0</v>
+        <f>'2、存量资产-y'!G25+'3、存量资产-k'!G13</f>
+        <v>8012723.4869999997</v>
       </c>
       <c r="O6" s="36">
         <v>8000000</v>
       </c>
-      <c r="P6" s="31"/>
+      <c r="P6" s="31">
+        <f t="shared" ref="P6:P7" si="0">N6/O6</f>
+        <v>1.0015904358750001</v>
+      </c>
     </row>
     <row r="7" spans="2:17" ht="24.65" customHeight="1">
       <c r="B7" s="17">
@@ -2751,13 +2751,8 @@
       <c r="K7" s="24"/>
       <c r="L7" s="25"/>
       <c r="M7" s="28"/>
-      <c r="N7" s="25">
-        <f>'2、存量资产-y'!B30+'3、存量资产-k'!B18</f>
-        <v>0</v>
-      </c>
-      <c r="O7" s="36">
-        <v>8000000</v>
-      </c>
+      <c r="N7" s="25"/>
+      <c r="O7" s="36"/>
       <c r="P7" s="31"/>
     </row>
     <row r="8" spans="2:17" ht="24.65" customHeight="1">
@@ -2876,47 +2871,47 @@
         <v>12</v>
       </c>
       <c r="C13" s="20">
-        <f>SUM(C3:C12)</f>
+        <f t="shared" ref="C13:L13" si="1">SUM(C3:C12)</f>
         <v>0</v>
       </c>
       <c r="D13" s="20">
-        <f>SUM(D3:D12)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="E13" s="20">
-        <f>SUM(E3:E12)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="F13" s="20">
-        <f>SUM(F3:F12)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G13" s="20">
-        <f>SUM(G3:G12)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H13" s="20">
-        <f>SUM(H3:H12)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I13" s="20">
-        <f>SUM(I3:I12)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J13" s="20">
-        <f>SUM(J3:J12)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="K13" s="26">
-        <f>SUM(K3:K12)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L13" s="27">
-        <f>SUM(L3:L12)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="M13" s="29" t="e">
-        <f t="shared" ref="M13" si="0">L13/J13</f>
+        <f t="shared" ref="M13" si="2">L13/J13</f>
         <v>#DIV/0!</v>
       </c>
       <c r="N13" s="27"/>
@@ -2928,35 +2923,35 @@
         <v>13</v>
       </c>
       <c r="C14" s="22" t="e">
-        <f t="shared" ref="C14:J14" si="1">C13/$J13</f>
+        <f t="shared" ref="C14:J14" si="3">C13/$J13</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D14" s="22" t="e">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
       <c r="E14" s="22" t="e">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
       <c r="F14" s="22" t="e">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G14" s="22" t="e">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H14" s="22" t="e">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I14" s="22" t="e">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
       <c r="J14" s="22" t="e">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
       <c r="K14" s="22"/>
@@ -3050,7 +3045,9 @@
       <c r="F2" s="6">
         <v>11830.94</v>
       </c>
-      <c r="G2" s="32"/>
+      <c r="G2" s="32">
+        <v>11832.74</v>
+      </c>
       <c r="H2" s="6"/>
       <c r="I2" s="6"/>
       <c r="J2" s="6"/>
@@ -3074,7 +3071,9 @@
       <c r="F3" s="7">
         <v>136231.75</v>
       </c>
-      <c r="G3" s="32"/>
+      <c r="G3" s="32">
+        <v>134522</v>
+      </c>
       <c r="H3" s="6"/>
       <c r="I3" s="7"/>
       <c r="J3" s="7"/>
@@ -3096,7 +3095,9 @@
       <c r="F4" s="6">
         <v>285165.96000000002</v>
       </c>
-      <c r="G4" s="33"/>
+      <c r="G4" s="33">
+        <v>284212</v>
+      </c>
       <c r="H4" s="6"/>
       <c r="I4" s="6"/>
       <c r="J4" s="6"/>
@@ -3120,7 +3121,9 @@
       <c r="F5" s="7">
         <v>0</v>
       </c>
-      <c r="G5" s="6"/>
+      <c r="G5" s="6">
+        <v>10537</v>
+      </c>
       <c r="H5" s="6"/>
       <c r="I5" s="7"/>
       <c r="J5" s="7"/>
@@ -3144,7 +3147,9 @@
       <c r="F6" s="6">
         <v>225255</v>
       </c>
-      <c r="G6" s="6"/>
+      <c r="G6" s="6">
+        <v>219972</v>
+      </c>
       <c r="H6" s="6"/>
       <c r="I6" s="6"/>
       <c r="J6" s="6"/>
@@ -3168,7 +3173,9 @@
       <c r="F7" s="6">
         <v>29456.53</v>
       </c>
-      <c r="G7" s="6"/>
+      <c r="G7" s="6">
+        <v>29884</v>
+      </c>
       <c r="H7" s="6"/>
       <c r="I7" s="6"/>
       <c r="J7" s="6"/>
@@ -3188,7 +3195,9 @@
       <c r="F8" s="6">
         <v>1471</v>
       </c>
-      <c r="G8" s="6"/>
+      <c r="G8" s="6">
+        <v>993.73</v>
+      </c>
       <c r="H8" s="6"/>
       <c r="I8" s="6"/>
       <c r="J8" s="6"/>
@@ -3212,7 +3221,9 @@
       <c r="F9" s="6">
         <v>0</v>
       </c>
-      <c r="G9" s="6"/>
+      <c r="G9" s="6">
+        <v>0</v>
+      </c>
       <c r="H9" s="6"/>
       <c r="I9" s="6"/>
       <c r="J9" s="6"/>
@@ -3320,7 +3331,9 @@
       <c r="F12" s="6">
         <v>19547.27</v>
       </c>
-      <c r="G12" s="6"/>
+      <c r="G12" s="6">
+        <v>19517</v>
+      </c>
       <c r="H12" s="6"/>
       <c r="I12" s="6"/>
       <c r="J12" s="7"/>
@@ -3344,7 +3357,9 @@
       <c r="F13" s="6">
         <v>361890.96</v>
       </c>
-      <c r="G13" s="6"/>
+      <c r="G13" s="6">
+        <v>362216</v>
+      </c>
       <c r="H13" s="6"/>
       <c r="I13" s="6"/>
       <c r="J13" s="6"/>
@@ -3368,7 +3383,9 @@
       <c r="F14" s="6">
         <v>31462</v>
       </c>
-      <c r="G14" s="6"/>
+      <c r="G14" s="6">
+        <v>31409</v>
+      </c>
       <c r="H14" s="6"/>
       <c r="I14" s="6"/>
       <c r="J14" s="6"/>
@@ -3392,7 +3409,9 @@
       <c r="F15" s="6">
         <v>99885.88</v>
       </c>
-      <c r="G15" s="6"/>
+      <c r="G15" s="6">
+        <v>99798</v>
+      </c>
       <c r="H15" s="6"/>
       <c r="I15" s="6"/>
       <c r="J15" s="6"/>
@@ -3406,51 +3425,51 @@
         <v>12</v>
       </c>
       <c r="B16" s="9">
-        <f>SUM(B2:B15)</f>
+        <f t="shared" ref="B16:M16" si="0">SUM(B2:B15)</f>
         <v>1846341.17</v>
       </c>
       <c r="C16" s="9">
-        <f>SUM(C2:C15)</f>
+        <f t="shared" si="0"/>
         <v>1896189.8</v>
       </c>
       <c r="D16" s="9">
-        <f>SUM(D2:D15)</f>
+        <f t="shared" si="0"/>
         <v>1000000</v>
       </c>
       <c r="E16" s="9">
-        <f>SUM(E2:E15)</f>
+        <f t="shared" si="0"/>
         <v>1000000</v>
       </c>
       <c r="F16" s="9">
-        <f>SUM(F2:F15)</f>
+        <f t="shared" si="0"/>
         <v>2202197.29</v>
       </c>
       <c r="G16" s="9">
         <f>SUM(G2:G15)</f>
+        <v>2204893.4699999997</v>
+      </c>
+      <c r="H16" s="9">
+        <f t="shared" si="0"/>
         <v>1000000</v>
       </c>
-      <c r="H16" s="9">
-        <f>SUM(H2:H15)</f>
+      <c r="I16" s="9">
+        <f t="shared" si="0"/>
         <v>1000000</v>
       </c>
-      <c r="I16" s="9">
-        <f>SUM(I2:I15)</f>
+      <c r="J16" s="9">
+        <f t="shared" si="0"/>
         <v>1000000</v>
       </c>
-      <c r="J16" s="9">
-        <f>SUM(J2:J15)</f>
+      <c r="K16" s="9">
+        <f t="shared" si="0"/>
         <v>1000000</v>
       </c>
-      <c r="K16" s="9">
-        <f>SUM(K2:K15)</f>
+      <c r="L16" s="9">
+        <f t="shared" si="0"/>
         <v>1000000</v>
       </c>
-      <c r="L16" s="9">
-        <f>SUM(L2:L15)</f>
-        <v>1000000</v>
-      </c>
       <c r="M16" s="9">
-        <f>SUM(M2:M15)</f>
+        <f t="shared" si="0"/>
         <v>1000000</v>
       </c>
       <c r="N16" s="15"/>
@@ -3470,7 +3489,9 @@
       <c r="F17" s="6">
         <v>136319</v>
       </c>
-      <c r="G17" s="6"/>
+      <c r="G17" s="6">
+        <v>136319</v>
+      </c>
       <c r="H17" s="6"/>
       <c r="I17" s="6"/>
       <c r="J17" s="6"/>
@@ -3494,7 +3515,9 @@
       <c r="F18" s="6">
         <v>151759</v>
       </c>
-      <c r="G18" s="6"/>
+      <c r="G18" s="6">
+        <v>151759</v>
+      </c>
       <c r="H18" s="6"/>
       <c r="I18" s="6"/>
       <c r="J18" s="6"/>
@@ -3518,7 +3541,9 @@
       <c r="F19" s="7">
         <v>22810</v>
       </c>
-      <c r="G19" s="7"/>
+      <c r="G19" s="7">
+        <v>22345</v>
+      </c>
       <c r="H19" s="7"/>
       <c r="I19" s="7"/>
       <c r="J19" s="7"/>
@@ -3536,15 +3561,15 @@
         <v>291297</v>
       </c>
       <c r="C20" s="11">
-        <f t="shared" ref="C20:M20" si="0">SUM(C17:C19)</f>
+        <f t="shared" ref="C20:M20" si="1">SUM(C17:C19)</f>
         <v>295477</v>
       </c>
       <c r="D20" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="E20" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="F20" s="11">
@@ -3552,31 +3577,31 @@
         <v>310888</v>
       </c>
       <c r="G20" s="11">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>310423</v>
       </c>
       <c r="H20" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I20" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J20" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="K20" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L20" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="M20" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="N20" s="15"/>
@@ -3628,7 +3653,7 @@
         <v>0</v>
       </c>
       <c r="C23" s="9">
-        <f t="shared" ref="C23:M23" si="1">SUM(C21:C22)</f>
+        <f t="shared" ref="C23:M23" si="2">SUM(C21:C22)</f>
         <v>0</v>
       </c>
       <c r="D23" s="9">
@@ -3636,39 +3661,39 @@
         <v>0</v>
       </c>
       <c r="E23" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F23" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G23" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="H23" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I23" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="J23" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K23" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L23" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="M23" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="N23" s="15"/>
@@ -3682,47 +3707,47 @@
         <v>2137638.17</v>
       </c>
       <c r="C24" s="13">
-        <f t="shared" ref="C24:M24" si="2">SUM(C16,C20)</f>
+        <f t="shared" ref="C24:M24" si="3">SUM(C16,C20)</f>
         <v>2191666.7999999998</v>
       </c>
       <c r="D24" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1000000</v>
       </c>
       <c r="E24" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1000000</v>
       </c>
       <c r="F24" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>2513085.29</v>
       </c>
       <c r="G24" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
+        <v>2515316.4699999997</v>
+      </c>
+      <c r="H24" s="13">
+        <f t="shared" si="3"/>
         <v>1000000</v>
       </c>
-      <c r="H24" s="13">
-        <f t="shared" si="2"/>
+      <c r="I24" s="13">
+        <f t="shared" si="3"/>
         <v>1000000</v>
       </c>
-      <c r="I24" s="13">
-        <f t="shared" si="2"/>
+      <c r="J24" s="13">
+        <f t="shared" si="3"/>
         <v>1000000</v>
       </c>
-      <c r="J24" s="13">
-        <f t="shared" si="2"/>
+      <c r="K24" s="13">
+        <f t="shared" si="3"/>
         <v>1000000</v>
       </c>
-      <c r="K24" s="13">
-        <f t="shared" si="2"/>
+      <c r="L24" s="13">
+        <f t="shared" si="3"/>
         <v>1000000</v>
       </c>
-      <c r="L24" s="13">
-        <f t="shared" si="2"/>
-        <v>1000000</v>
-      </c>
       <c r="M24" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1000000</v>
       </c>
       <c r="N24" s="15"/>
@@ -3736,47 +3761,47 @@
         <v>2137638.17</v>
       </c>
       <c r="C25" s="13">
-        <f t="shared" ref="C25:M25" si="3">C24-C23</f>
+        <f t="shared" ref="C25:M25" si="4">C24-C23</f>
         <v>2191666.7999999998</v>
       </c>
       <c r="D25" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1000000</v>
       </c>
       <c r="E25" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1000000</v>
       </c>
       <c r="F25" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2513085.29</v>
       </c>
       <c r="G25" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
+        <v>2515316.4699999997</v>
+      </c>
+      <c r="H25" s="13">
+        <f t="shared" si="4"/>
         <v>1000000</v>
       </c>
-      <c r="H25" s="13">
-        <f t="shared" si="3"/>
+      <c r="I25" s="13">
+        <f t="shared" si="4"/>
         <v>1000000</v>
       </c>
-      <c r="I25" s="13">
-        <f t="shared" si="3"/>
+      <c r="J25" s="13">
+        <f t="shared" si="4"/>
         <v>1000000</v>
       </c>
-      <c r="J25" s="13">
-        <f t="shared" si="3"/>
+      <c r="K25" s="13">
+        <f t="shared" si="4"/>
         <v>1000000</v>
       </c>
-      <c r="K25" s="13">
-        <f t="shared" si="3"/>
+      <c r="L25" s="13">
+        <f t="shared" si="4"/>
         <v>1000000</v>
       </c>
-      <c r="L25" s="13">
-        <f t="shared" si="3"/>
-        <v>1000000</v>
-      </c>
       <c r="M25" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1000000</v>
       </c>
       <c r="N25" s="15"/>
@@ -3864,7 +3889,10 @@
         <f>602516*7</f>
         <v>4217612</v>
       </c>
-      <c r="G2" s="6"/>
+      <c r="G2" s="6">
+        <f>708815*6.7838</f>
+        <v>4808459.1970000006</v>
+      </c>
       <c r="H2" s="6"/>
       <c r="I2" s="6"/>
       <c r="J2" s="6"/>
@@ -3890,7 +3918,10 @@
       <c r="F3" s="7">
         <v>626003</v>
       </c>
-      <c r="G3" s="7"/>
+      <c r="G3" s="7">
+        <f>58877.21+476635.39</f>
+        <v>535512.6</v>
+      </c>
       <c r="H3" s="7"/>
       <c r="I3" s="7"/>
       <c r="J3" s="7"/>
@@ -3915,7 +3946,10 @@
         <f>15023+3705</f>
         <v>18728</v>
       </c>
-      <c r="G4" s="6"/>
+      <c r="G4" s="6">
+        <f>3499.22+33235</f>
+        <v>36734.22</v>
+      </c>
       <c r="H4" s="6"/>
       <c r="I4" s="6"/>
       <c r="J4" s="6"/>
@@ -3950,7 +3984,7 @@
       </c>
       <c r="G5" s="9">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>5380706.017</v>
       </c>
       <c r="H5" s="9">
         <f t="shared" si="0"/>
@@ -3996,7 +4030,10 @@
         <f>23429+58692+35826</f>
         <v>117947</v>
       </c>
-      <c r="G6" s="6"/>
+      <c r="G6" s="6">
+        <f>13429+58692+21128</f>
+        <v>93249</v>
+      </c>
       <c r="H6" s="6"/>
       <c r="I6" s="6"/>
       <c r="J6" s="6"/>
@@ -4020,7 +4057,9 @@
       <c r="F7" s="6">
         <v>23538</v>
       </c>
-      <c r="G7" s="6"/>
+      <c r="G7" s="6">
+        <v>23452</v>
+      </c>
       <c r="H7" s="6"/>
       <c r="I7" s="6"/>
       <c r="J7" s="6"/>
@@ -4055,7 +4094,7 @@
       </c>
       <c r="G8" s="11">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>116701</v>
       </c>
       <c r="H8" s="11">
         <f t="shared" si="1"/>
@@ -4163,7 +4202,7 @@
       </c>
       <c r="G12" s="13">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>5497407.017</v>
       </c>
       <c r="H12" s="13">
         <f t="shared" si="2"/>
@@ -4217,7 +4256,7 @@
       </c>
       <c r="G13" s="13">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>5497407.017</v>
       </c>
       <c r="H13" s="13">
         <f t="shared" si="3"/>
